--- a/dist/成果/沟道横断面成果表_AFAE900122HF0000ZBCS014.xlsx
+++ b/dist/成果/沟道横断面成果表_AFAE900122HF0000ZBCS014.xlsx
@@ -2180,22 +2180,22 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="E4:G4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E4:G4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"上游,下游,控制断面"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:C5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5:C5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"矩形,抛物线型,三角形,复合型"</formula1>
     </dataValidation>
-    <dataValidation sqref="B6:C6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B6:C6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"岩石,砂砾石,砂土,壤土,粘土"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7:C7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7:C7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
